--- a/02 - config/example_big/agents.xlsx
+++ b/02 - config/example_big/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="294">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -459,357 +459,363 @@
     <t>meter/prob_missing</t>
   </si>
   <si>
-    <t>CAQ4qbKndqVO5KP</t>
-  </si>
-  <si>
-    <t>P05FuuJKAHoBtll</t>
-  </si>
-  <si>
-    <t>38JpW7PalZEayze</t>
-  </si>
-  <si>
-    <t>OrzVnFyFf8KDWZb</t>
-  </si>
-  <si>
-    <t>0jX330LTbs2R0pg</t>
-  </si>
-  <si>
-    <t>qm3wd3abNgNc06L</t>
-  </si>
-  <si>
-    <t>JbNr6emSGvLnXxr</t>
-  </si>
-  <si>
-    <t>fpCwBkrz7WURF2f</t>
-  </si>
-  <si>
-    <t>mlNdcfxpXKZxCp7</t>
-  </si>
-  <si>
-    <t>bGXeG7MNEBuSaN5</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
+    <t>CbexoZi4qm8D0Zc</t>
+  </si>
+  <si>
+    <t>aG3SyfMfhy3mHmP</t>
+  </si>
+  <si>
+    <t>jFURx0Lil3RSKR0</t>
+  </si>
+  <si>
+    <t>xtL6fGWkujPMeq3</t>
+  </si>
+  <si>
+    <t>0lNKjYQAP2yc8OD</t>
+  </si>
+  <si>
+    <t>99WJQyTvUPPcw5h</t>
+  </si>
+  <si>
+    <t>hSGEpfFSIvUZND9</t>
+  </si>
+  <si>
+    <t>f6j6zw4S96gvNA0</t>
+  </si>
+  <si>
+    <t>qjPm2il391BNsHD</t>
+  </si>
+  <si>
+    <t>AuguuDTKAfMfA41</t>
+  </si>
+  <si>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
-    <t>hh_2532_0.csv</t>
-  </si>
-  <si>
     <t>hh_4536_0.csv</t>
   </si>
   <si>
     <t>hh_3648_0.csv</t>
   </si>
   <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>naive_average</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>heat_2687_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2012_3.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_4536_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_config.json</t>
+  </si>
+  <si>
+    <t>smoothed</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
+  </si>
+  <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_41.csv</t>
+  </si>
+  <si>
+    <t>price_sensitive</t>
+  </si>
+  <si>
+    <t>ev_close</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
+    <t>vutoQyhLMOcs2Jw</t>
+  </si>
+  <si>
+    <t>ggrAzbXks782JvB</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>1yEfSiKpaomiSJt</t>
+  </si>
+  <si>
+    <t>Qxj1ccJswBostlw</t>
+  </si>
+  <si>
+    <t>0e7auEOnWphCJeX</t>
+  </si>
+  <si>
+    <t>H5GfqhLn9fCXzdh</t>
+  </si>
+  <si>
+    <t>2opnkZbKOEcNmJZ</t>
+  </si>
+  <si>
+    <t>1v2tD6aTEFMop1H</t>
+  </si>
+  <si>
+    <t>DcRAC5EafjR5z77</t>
+  </si>
+  <si>
+    <t>vMkxCH1gK5XqeEO</t>
+  </si>
+  <si>
+    <t>PqNQUMtmOCyDkqu</t>
+  </si>
+  <si>
+    <t>cVivoURlWnTwNIW</t>
+  </si>
+  <si>
+    <t>4iDdQBxnutgPHo1</t>
+  </si>
+  <si>
+    <t>BbuuTysUSo9FMdP</t>
+  </si>
+  <si>
+    <t>fjtT81mG3c8crBj</t>
+  </si>
+  <si>
+    <t>8DGWUwR0YSyawcq</t>
+  </si>
+  <si>
     <t>hh_2455_0.csv</t>
   </si>
   <si>
-    <t>naive_average</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+    <t>hh_1720_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1266_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1546_2.csv</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2896_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1009_1.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
   </si>
   <si>
     <t>heat_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4536_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2455_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_config.json</t>
-  </si>
-  <si>
-    <t>smoothed</t>
-  </si>
-  <si>
-    <t>green_local</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
+    <t>pv_2_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>fixed_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_42.csv</t>
   </si>
   <si>
     <t>ev_parttime_90.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_42.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_43.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
-  </si>
-  <si>
-    <t>ev_close</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>fIN6RLaCSLIs34X</t>
-  </si>
-  <si>
-    <t>faG89XBS8LQGBIT</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>DPpRmoJAzEyUctg</t>
-  </si>
-  <si>
-    <t>eDCcydDkFdMhdg6</t>
-  </si>
-  <si>
-    <t>Zt7eMmbkydw68ro</t>
-  </si>
-  <si>
-    <t>b1bKdSrNn09lvTL</t>
-  </si>
-  <si>
-    <t>WDMMWj3CdvUYmAc</t>
-  </si>
-  <si>
-    <t>Rly2SV5bAywPsti</t>
-  </si>
-  <si>
-    <t>h0EK54BR0dStnX6</t>
-  </si>
-  <si>
-    <t>LWywX8b1UW7qsIv</t>
-  </si>
-  <si>
-    <t>n1aHpiesYKwTEdw</t>
-  </si>
-  <si>
-    <t>GXOwNhY6LN4QB5k</t>
-  </si>
-  <si>
-    <t>mI1HMp7xzXEQPVM</t>
-  </si>
-  <si>
-    <t>ligakxWTagqsUtW</t>
-  </si>
-  <si>
-    <t>2u0caNRWq8dkQXY</t>
-  </si>
-  <si>
-    <t>LLV6xoRvQ98GtrC</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1720_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1158_4.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1546_2.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_2896_0.csv</t>
-  </si>
-  <si>
-    <t>hh_945_1.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_2_pu.csv</t>
+    <t>ev_fulltime_49.csv</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>general/parameters/type</t>
+  </si>
+  <si>
+    <t>general/fcast_retraining_frequency</t>
+  </si>
+  <si>
+    <t>zroNiiCe0GBCL2g</t>
+  </si>
+  <si>
+    <t>uSpTda3baDryzyi</t>
+  </si>
+  <si>
+    <t>AHxxivSKpippvvg</t>
+  </si>
+  <si>
+    <t>g2c72bTBUkns839</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>office_pu_0.csv</t>
+  </si>
+  <si>
+    <t>retail_pu_0.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>9Iv1qVtDrH8b06h</t>
+  </si>
+  <si>
+    <t>43cmHFwuwaTpW5J</t>
+  </si>
+  <si>
+    <t>tobacco</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>tobacco_pu_0.csv</t>
+  </si>
+  <si>
+    <t>food_pu_0.csv</t>
+  </si>
+  <si>
+    <t>R5EKnaf9eQmFF0J</t>
+  </si>
+  <si>
+    <t>XVa8gEvJKsAmeLd</t>
+  </si>
+  <si>
+    <t>uBhuMZ3jeMafpsA</t>
+  </si>
+  <si>
+    <t>ZmtU6It7cUgj0JY</t>
+  </si>
+  <si>
+    <t>CxR1oqbqIf9LamV</t>
+  </si>
+  <si>
+    <t>m8PnE8oAxkCt7c1</t>
   </si>
   <si>
     <t>pv_3_pu.csv</t>
   </si>
   <si>
-    <t>fixed_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>general/parameters/type</t>
-  </si>
-  <si>
-    <t>general/fcast_retraining_frequency</t>
-  </si>
-  <si>
-    <t>MiMOLDWdvO8Wy78</t>
-  </si>
-  <si>
-    <t>LmWc11DTOn0d34C</t>
-  </si>
-  <si>
-    <t>pR9hLQSVdZLInjy</t>
-  </si>
-  <si>
-    <t>d6WTzfkMUtlLlDo</t>
-  </si>
-  <si>
-    <t>retail</t>
-  </si>
-  <si>
-    <t>office</t>
-  </si>
-  <si>
-    <t>retail_pu_0.csv</t>
-  </si>
-  <si>
-    <t>office_pu_0.csv</t>
-  </si>
-  <si>
-    <t>pv_1_pu.csv</t>
-  </si>
-  <si>
-    <t>QnFhm1Pv1aaVe0g</t>
-  </si>
-  <si>
-    <t>QOE3HKoozDCq8tw</t>
-  </si>
-  <si>
-    <t>tobacco</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>tobacco_pu_0.csv</t>
-  </si>
-  <si>
-    <t>food_pu_0.csv</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>kWZJYPkjAMgoDTy</t>
-  </si>
-  <si>
-    <t>Xt6DSBzm6ZkFE2b</t>
-  </si>
-  <si>
-    <t>e4NO5d4L5ogT5e1</t>
-  </si>
-  <si>
-    <t>kHfE5aklazt9gY8</t>
-  </si>
-  <si>
-    <t>MbYREwE6tBPw9O8</t>
-  </si>
-  <si>
-    <t>BDhRg5rXQtx9OCW</t>
-  </si>
-  <si>
     <t>psh/owner</t>
   </si>
   <si>
@@ -870,31 +876,31 @@
     <t>hydrogen/quality</t>
   </si>
   <si>
-    <t>VpVR0SQWDVXCpS0</t>
-  </si>
-  <si>
-    <t>sKBLdqZTKGHC4b4</t>
-  </si>
-  <si>
-    <t>PKrckh0Gawj8Y7F</t>
-  </si>
-  <si>
-    <t>Mc1s4lH5J7oAYcD</t>
-  </si>
-  <si>
-    <t>ZnZ0VFZkWBQuGen</t>
-  </si>
-  <si>
-    <t>0UaMMVpfNCH8L0A</t>
-  </si>
-  <si>
-    <t>N7C5Izpti9DJles</t>
-  </si>
-  <si>
-    <t>pLVa3kyoqiBUhUx</t>
-  </si>
-  <si>
-    <t>yAHbtlZFRelcTi6</t>
+    <t>FcA5k3bmzdPDw6d</t>
+  </si>
+  <si>
+    <t>KMQiDJtxSmL0KUh</t>
+  </si>
+  <si>
+    <t>TxTqzNHvWeglOtg</t>
+  </si>
+  <si>
+    <t>1Zyp0JqLgNp8pjC</t>
+  </si>
+  <si>
+    <t>bgCPDb87tpOldEi</t>
+  </si>
+  <si>
+    <t>KMzbxGDXRcXyncj</t>
+  </si>
+  <si>
+    <t>etHm4s2whU7L0ei</t>
+  </si>
+  <si>
+    <t>OsUwiSrPFtJQqbQ</t>
+  </si>
+  <si>
+    <t>3moFz4UqRzgfDNk</t>
   </si>
 </sst>
 </file>
@@ -1703,10 +1709,10 @@
         <v>146</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1715,7 +1721,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1730,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <v>3564000</v>
+        <v>2687000</v>
       </c>
       <c r="P2" t="s">
         <v>156</v>
@@ -1781,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="AH2">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI2" t="s">
         <v>164</v>
@@ -1814,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="AS2">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="AT2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AU2">
         <v>55</v>
@@ -1838,31 +1844,16 @@
         <v>90</v>
       </c>
       <c r="BA2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="b">
         <v>1</v>
       </c>
-      <c r="BD2">
-        <v>5800</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF2">
-        <v>0</v>
-      </c>
-      <c r="BG2">
-        <v>40</v>
-      </c>
-      <c r="BH2" t="b">
-        <v>1</v>
-      </c>
       <c r="BI2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ2">
         <v>2</v>
@@ -1871,29 +1862,38 @@
         <v>9</v>
       </c>
       <c r="BL2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="b">
         <v>1</v>
       </c>
+      <c r="BP2">
+        <v>1100</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>182</v>
+      </c>
+      <c r="BR2" t="b">
+        <v>1</v>
+      </c>
       <c r="BS2" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT2">
+        <v>2</v>
+      </c>
+      <c r="BU2">
+        <v>9</v>
+      </c>
+      <c r="BV2" t="s">
         <v>181</v>
       </c>
-      <c r="BT2">
-        <v>2</v>
-      </c>
-      <c r="BU2">
-        <v>9</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>177</v>
-      </c>
       <c r="BW2">
         <v>0</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="CC2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD2">
         <v>2</v>
@@ -1913,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="CF2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1925,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM2">
         <v>1</v>
@@ -1937,22 +1937,22 @@
         <v>1</v>
       </c>
       <c r="CP2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="CQ2">
+        <v>75000</v>
+      </c>
+      <c r="CR2">
+        <v>20000</v>
+      </c>
+      <c r="CS2">
+        <v>7200</v>
+      </c>
+      <c r="CT2">
+        <v>11000</v>
+      </c>
+      <c r="CU2">
         <v>100000</v>
-      </c>
-      <c r="CR2">
-        <v>25000</v>
-      </c>
-      <c r="CS2">
-        <v>11000</v>
-      </c>
-      <c r="CT2">
-        <v>22000</v>
-      </c>
-      <c r="CU2">
-        <v>200000</v>
       </c>
       <c r="CV2">
         <v>0.9</v>
@@ -1967,22 +1967,22 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="DA2">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="DB2">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="DC2">
         <v>7200</v>
       </c>
       <c r="DD2">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="DE2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="DF2">
         <v>0.9</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK2">
         <v>0.05</v>
@@ -2012,10 +2012,10 @@
         <v>8.5</v>
       </c>
       <c r="DO2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ2">
         <v>0</v>
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="DS2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2036,28 +2036,28 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ2">
         <v>96</v>
       </c>
       <c r="EK2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="EM2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="EO2">
         <v>0</v>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <v>5527000</v>
+        <v>2012000</v>
       </c>
       <c r="P3" t="s">
         <v>157</v>
@@ -2161,7 +2161,7 @@
         <v>165</v>
       </c>
       <c r="AJ3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="s">
         <v>162</v>
@@ -2188,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="AT3" t="s">
         <v>172</v>
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="BI3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ3">
         <v>2</v>
@@ -2230,7 +2230,7 @@
         <v>9</v>
       </c>
       <c r="BL3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM3">
         <v>0</v>
@@ -2242,17 +2242,17 @@
         <v>1</v>
       </c>
       <c r="BS3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT3">
+        <v>2</v>
+      </c>
+      <c r="BU3">
+        <v>9</v>
+      </c>
+      <c r="BV3" t="s">
         <v>181</v>
       </c>
-      <c r="BT3">
-        <v>2</v>
-      </c>
-      <c r="BU3">
-        <v>9</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>177</v>
-      </c>
       <c r="BW3">
         <v>0</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="CC3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD3">
         <v>2</v>
@@ -2272,7 +2272,7 @@
         <v>9</v>
       </c>
       <c r="CF3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="DJ3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK3">
         <v>0.05</v>
@@ -2311,10 +2311,10 @@
         <v>8.5</v>
       </c>
       <c r="DO3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ3">
         <v>0</v>
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="DS3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA3">
         <v>0</v>
@@ -2335,28 +2335,28 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ3">
         <v>96</v>
       </c>
       <c r="EK3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EM3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EO3">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>148</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -2388,7 +2388,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2403,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="O4">
-        <v>2532000</v>
+        <v>5527000</v>
       </c>
       <c r="P4" t="s">
         <v>158</v>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI4" t="s">
         <v>166</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="AT4" t="s">
         <v>173</v>
@@ -2520,10 +2520,10 @@
         <v>1</v>
       </c>
       <c r="BD4">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="BE4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ4">
         <v>2</v>
@@ -2544,7 +2544,7 @@
         <v>9</v>
       </c>
       <c r="BL4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM4">
         <v>1</v>
@@ -2556,26 +2556,26 @@
         <v>1</v>
       </c>
       <c r="BP4">
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="BQ4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="BR4" t="b">
         <v>1</v>
       </c>
       <c r="BS4" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT4">
+        <v>2</v>
+      </c>
+      <c r="BU4">
+        <v>9</v>
+      </c>
+      <c r="BV4" t="s">
         <v>181</v>
       </c>
-      <c r="BT4">
-        <v>2</v>
-      </c>
-      <c r="BU4">
-        <v>9</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>177</v>
-      </c>
       <c r="BW4">
         <v>0</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="CC4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD4">
         <v>2</v>
@@ -2595,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="CF4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG4">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM4">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="CQ4">
         <v>50000</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="DJ4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK4">
         <v>0.05</v>
@@ -2664,10 +2664,10 @@
         <v>8.5</v>
       </c>
       <c r="DO4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -2676,13 +2676,13 @@
         <v>1</v>
       </c>
       <c r="DS4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT4">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DU4">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DV4">
         <v>0.95</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="DZ4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA4">
         <v>0</v>
@@ -2706,28 +2706,28 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ4">
         <v>96</v>
       </c>
       <c r="EK4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL4">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="EO4">
         <v>0</v>
@@ -2747,10 +2747,10 @@
         <v>149</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2759,7 +2759,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2825,7 +2825,7 @@
         <v>1</v>
       </c>
       <c r="AH5">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI5" t="s">
         <v>167</v>
@@ -2858,10 +2858,10 @@
         <v>1</v>
       </c>
       <c r="AS5">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="AT5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AU5">
         <v>55</v>
@@ -2891,22 +2891,22 @@
         <v>1</v>
       </c>
       <c r="BD5">
-        <v>6400</v>
+        <v>7400</v>
       </c>
       <c r="BE5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="b">
         <v>1</v>
       </c>
       <c r="BI5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ5">
         <v>2</v>
@@ -2915,7 +2915,7 @@
         <v>9</v>
       </c>
       <c r="BL5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM5">
         <v>1</v>
@@ -2927,26 +2927,26 @@
         <v>1</v>
       </c>
       <c r="BP5">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="BQ5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="BR5" t="b">
         <v>1</v>
       </c>
       <c r="BS5" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT5">
+        <v>2</v>
+      </c>
+      <c r="BU5">
+        <v>9</v>
+      </c>
+      <c r="BV5" t="s">
         <v>181</v>
       </c>
-      <c r="BT5">
-        <v>2</v>
-      </c>
-      <c r="BU5">
-        <v>9</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>177</v>
-      </c>
       <c r="BW5">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="CC5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD5">
         <v>2</v>
@@ -2966,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="CF5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -2978,19 +2978,49 @@
         <v>1</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO5" t="b">
         <v>1</v>
       </c>
+      <c r="CP5" t="s">
+        <v>190</v>
+      </c>
+      <c r="CQ5">
+        <v>100000</v>
+      </c>
+      <c r="CR5">
+        <v>25000</v>
+      </c>
+      <c r="CS5">
+        <v>11000</v>
+      </c>
+      <c r="CT5">
+        <v>22000</v>
+      </c>
+      <c r="CU5">
+        <v>200000</v>
+      </c>
+      <c r="CV5">
+        <v>0.9</v>
+      </c>
+      <c r="CW5">
+        <v>0.8</v>
+      </c>
+      <c r="CX5" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK5">
         <v>0.05</v>
@@ -3005,10 +3035,10 @@
         <v>8.5</v>
       </c>
       <c r="DO5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ5">
         <v>0</v>
@@ -3017,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="DS5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA5">
         <v>0</v>
@@ -3029,28 +3059,28 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ5">
         <v>96</v>
       </c>
       <c r="EK5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="EM5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EO5">
         <v>0</v>
@@ -3070,10 +3100,10 @@
         <v>150</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3082,7 +3112,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3097,10 +3127,10 @@
         <v>1</v>
       </c>
       <c r="O6">
-        <v>5527000</v>
+        <v>3648000</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q6" t="s">
         <v>162</v>
@@ -3148,10 +3178,10 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AJ6">
         <v>55</v>
@@ -3181,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="AS6">
-        <v>3200000</v>
+        <v>2100000</v>
       </c>
       <c r="AT6" t="s">
         <v>173</v>
@@ -3205,16 +3235,31 @@
         <v>90</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="b">
         <v>1</v>
       </c>
+      <c r="BD6">
+        <v>6300</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>40</v>
+      </c>
+      <c r="BH6" t="b">
+        <v>1</v>
+      </c>
       <c r="BI6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ6">
         <v>2</v>
@@ -3223,7 +3268,7 @@
         <v>9</v>
       </c>
       <c r="BL6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM6">
         <v>0</v>
@@ -3235,17 +3280,17 @@
         <v>1</v>
       </c>
       <c r="BS6" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT6">
+        <v>2</v>
+      </c>
+      <c r="BU6">
+        <v>9</v>
+      </c>
+      <c r="BV6" t="s">
         <v>181</v>
       </c>
-      <c r="BT6">
-        <v>2</v>
-      </c>
-      <c r="BU6">
-        <v>9</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>177</v>
-      </c>
       <c r="BW6">
         <v>0</v>
       </c>
@@ -3256,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="CC6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD6">
         <v>2</v>
@@ -3265,7 +3310,7 @@
         <v>9</v>
       </c>
       <c r="CF6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -3277,49 +3322,19 @@
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="b">
         <v>1</v>
       </c>
-      <c r="CP6" t="s">
-        <v>185</v>
-      </c>
-      <c r="CQ6">
-        <v>50000</v>
-      </c>
-      <c r="CR6">
-        <v>15000</v>
-      </c>
-      <c r="CS6">
-        <v>7200</v>
-      </c>
-      <c r="CT6">
-        <v>7200</v>
-      </c>
-      <c r="CU6">
-        <v>50000</v>
-      </c>
-      <c r="CV6">
-        <v>0.9</v>
-      </c>
-      <c r="CW6">
-        <v>0.8</v>
-      </c>
-      <c r="CX6" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY6" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK6">
         <v>0.05</v>
@@ -3334,10 +3349,10 @@
         <v>8.5</v>
       </c>
       <c r="DO6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ6">
         <v>0</v>
@@ -3346,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="DS6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA6">
         <v>0</v>
@@ -3358,25 +3373,25 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ6">
         <v>96</v>
       </c>
       <c r="EK6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL6">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EM6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN6">
         <v>20</v>
@@ -3399,10 +3414,10 @@
         <v>151</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3411,7 +3426,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3477,13 +3492,13 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK7" t="s">
         <v>162</v>
@@ -3510,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="AT7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AU7">
         <v>55</v>
@@ -3543,22 +3558,22 @@
         <v>1</v>
       </c>
       <c r="BD7">
-        <v>5000</v>
+        <v>4600</v>
       </c>
       <c r="BE7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="BG7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="b">
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ7">
         <v>2</v>
@@ -3567,7 +3582,7 @@
         <v>9</v>
       </c>
       <c r="BL7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM7">
         <v>0</v>
@@ -3579,17 +3594,17 @@
         <v>1</v>
       </c>
       <c r="BS7" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT7">
+        <v>2</v>
+      </c>
+      <c r="BU7">
+        <v>9</v>
+      </c>
+      <c r="BV7" t="s">
         <v>181</v>
       </c>
-      <c r="BT7">
-        <v>2</v>
-      </c>
-      <c r="BU7">
-        <v>9</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>177</v>
-      </c>
       <c r="BW7">
         <v>0</v>
       </c>
@@ -3600,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="CC7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD7">
         <v>2</v>
@@ -3609,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="CF7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3621,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="CL7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM7">
         <v>0</v>
@@ -3633,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="DJ7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK7">
         <v>0.05</v>
@@ -3648,10 +3663,10 @@
         <v>8.5</v>
       </c>
       <c r="DO7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ7">
         <v>1</v>
@@ -3660,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="DS7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT7">
         <v>3600</v>
@@ -3681,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA7">
         <v>0</v>
@@ -3690,28 +3705,28 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ7">
         <v>96</v>
       </c>
       <c r="EK7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL7">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="EM7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="EO7">
         <v>0</v>
@@ -3731,10 +3746,10 @@
         <v>152</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -3743,7 +3758,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -3758,10 +3773,10 @@
         <v>1</v>
       </c>
       <c r="O8">
-        <v>2455000</v>
+        <v>5527000</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="s">
         <v>162</v>
@@ -3809,10 +3824,10 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AJ8">
         <v>55</v>
@@ -3842,10 +3857,10 @@
         <v>1</v>
       </c>
       <c r="AS8">
-        <v>2800000</v>
+        <v>1800000</v>
       </c>
       <c r="AT8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AU8">
         <v>55</v>
@@ -3875,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="BD8">
-        <v>3500</v>
+        <v>7300</v>
       </c>
       <c r="BE8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF8">
         <v>0</v>
@@ -3890,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="BI8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ8">
         <v>2</v>
@@ -3899,7 +3914,7 @@
         <v>9</v>
       </c>
       <c r="BL8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM8">
         <v>1</v>
@@ -3911,26 +3926,26 @@
         <v>1</v>
       </c>
       <c r="BP8">
-        <v>1400</v>
+        <v>4100</v>
       </c>
       <c r="BQ8" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="BR8" t="b">
         <v>1</v>
       </c>
       <c r="BS8" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT8">
+        <v>2</v>
+      </c>
+      <c r="BU8">
+        <v>9</v>
+      </c>
+      <c r="BV8" t="s">
         <v>181</v>
       </c>
-      <c r="BT8">
-        <v>2</v>
-      </c>
-      <c r="BU8">
-        <v>9</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>177</v>
-      </c>
       <c r="BW8">
         <v>0</v>
       </c>
@@ -3941,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="CC8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD8">
         <v>2</v>
@@ -3950,7 +3965,7 @@
         <v>9</v>
       </c>
       <c r="CF8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -3962,19 +3977,49 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO8" t="b">
         <v>1</v>
       </c>
+      <c r="CP8" t="s">
+        <v>191</v>
+      </c>
+      <c r="CQ8">
+        <v>75000</v>
+      </c>
+      <c r="CR8">
+        <v>20000</v>
+      </c>
+      <c r="CS8">
+        <v>7200</v>
+      </c>
+      <c r="CT8">
+        <v>11000</v>
+      </c>
+      <c r="CU8">
+        <v>100000</v>
+      </c>
+      <c r="CV8">
+        <v>0.9</v>
+      </c>
+      <c r="CW8">
+        <v>0.8</v>
+      </c>
+      <c r="CX8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK8">
         <v>0.05</v>
@@ -3989,10 +4034,10 @@
         <v>8.5</v>
       </c>
       <c r="DO8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ8">
         <v>1</v>
@@ -4001,13 +4046,13 @@
         <v>1</v>
       </c>
       <c r="DS8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT8">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DU8">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DV8">
         <v>0.95</v>
@@ -4022,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="DZ8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA8">
         <v>0</v>
@@ -4031,25 +4076,25 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ8">
         <v>96</v>
       </c>
       <c r="EK8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL8">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="EM8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN8">
         <v>10</v>
@@ -4099,10 +4144,10 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>4536000</v>
+        <v>3648000</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q9" t="s">
         <v>162</v>
@@ -4153,10 +4198,10 @@
         <v>19500000</v>
       </c>
       <c r="AI9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AJ9">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="s">
         <v>162</v>
@@ -4186,7 +4231,7 @@
         <v>2400000</v>
       </c>
       <c r="AT9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AU9">
         <v>55</v>
@@ -4216,22 +4261,22 @@
         <v>1</v>
       </c>
       <c r="BD9">
-        <v>6200</v>
+        <v>5600</v>
       </c>
       <c r="BE9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH9" t="b">
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ9">
         <v>2</v>
@@ -4240,7 +4285,7 @@
         <v>9</v>
       </c>
       <c r="BL9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM9">
         <v>1</v>
@@ -4252,38 +4297,38 @@
         <v>1</v>
       </c>
       <c r="BP9">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="BQ9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BR9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT9">
+        <v>2</v>
+      </c>
+      <c r="BU9">
+        <v>9</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>181</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC9" t="s">
         <v>180</v>
       </c>
-      <c r="BR9" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT9">
-        <v>2</v>
-      </c>
-      <c r="BU9">
-        <v>9</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>176</v>
-      </c>
       <c r="CD9">
         <v>2</v>
       </c>
@@ -4291,7 +4336,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4303,49 +4348,19 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO9" t="b">
         <v>1</v>
       </c>
-      <c r="CP9" t="s">
-        <v>186</v>
-      </c>
-      <c r="CQ9">
-        <v>75000</v>
-      </c>
-      <c r="CR9">
-        <v>20000</v>
-      </c>
-      <c r="CS9">
-        <v>7200</v>
-      </c>
-      <c r="CT9">
-        <v>11000</v>
-      </c>
-      <c r="CU9">
-        <v>100000</v>
-      </c>
-      <c r="CV9">
-        <v>0.9</v>
-      </c>
-      <c r="CW9">
-        <v>0.8</v>
-      </c>
-      <c r="CX9" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY9" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK9">
         <v>0.05</v>
@@ -4360,10 +4375,10 @@
         <v>8.5</v>
       </c>
       <c r="DO9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ9">
         <v>1</v>
@@ -4372,13 +4387,13 @@
         <v>1</v>
       </c>
       <c r="DS9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT9">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="DU9">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="DV9">
         <v>0.95</v>
@@ -4393,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="DZ9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA9">
         <v>0</v>
@@ -4402,28 +4417,28 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ9">
         <v>96</v>
       </c>
       <c r="EK9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL9">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="EM9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="EO9">
         <v>0</v>
@@ -4443,10 +4458,10 @@
         <v>154</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -4455,7 +4470,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4470,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>4536000</v>
+        <v>3296000</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10" t="s">
         <v>162</v>
@@ -4521,10 +4536,10 @@
         <v>1</v>
       </c>
       <c r="AH10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AJ10">
         <v>55</v>
@@ -4554,10 +4569,10 @@
         <v>1</v>
       </c>
       <c r="AS10">
-        <v>2100000</v>
+        <v>3200000</v>
       </c>
       <c r="AT10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AU10">
         <v>55</v>
@@ -4587,22 +4602,22 @@
         <v>1</v>
       </c>
       <c r="BD10">
-        <v>5800</v>
+        <v>4000</v>
       </c>
       <c r="BE10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="b">
         <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ10">
         <v>2</v>
@@ -4611,38 +4626,29 @@
         <v>9</v>
       </c>
       <c r="BL10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="b">
         <v>1</v>
       </c>
-      <c r="BP10">
-        <v>2400</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR10" t="b">
-        <v>1</v>
-      </c>
       <c r="BS10" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT10">
+        <v>2</v>
+      </c>
+      <c r="BU10">
+        <v>9</v>
+      </c>
+      <c r="BV10" t="s">
         <v>181</v>
       </c>
-      <c r="BT10">
-        <v>2</v>
-      </c>
-      <c r="BU10">
-        <v>9</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>177</v>
-      </c>
       <c r="BW10">
         <v>0</v>
       </c>
@@ -4653,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="CC10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD10">
         <v>2</v>
@@ -4662,7 +4668,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -4674,19 +4680,49 @@
         <v>1</v>
       </c>
       <c r="CL10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO10" t="b">
         <v>1</v>
       </c>
+      <c r="CP10" t="s">
+        <v>189</v>
+      </c>
+      <c r="CQ10">
+        <v>50000</v>
+      </c>
+      <c r="CR10">
+        <v>15000</v>
+      </c>
+      <c r="CS10">
+        <v>7200</v>
+      </c>
+      <c r="CT10">
+        <v>7200</v>
+      </c>
+      <c r="CU10">
+        <v>50000</v>
+      </c>
+      <c r="CV10">
+        <v>0.9</v>
+      </c>
+      <c r="CW10">
+        <v>0.8</v>
+      </c>
+      <c r="CX10" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK10">
         <v>0.05</v>
@@ -4701,10 +4737,10 @@
         <v>8.5</v>
       </c>
       <c r="DO10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ10">
         <v>1</v>
@@ -4713,13 +4749,13 @@
         <v>1</v>
       </c>
       <c r="DS10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT10">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="DU10">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="DV10">
         <v>0.95</v>
@@ -4734,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="DZ10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA10">
         <v>0</v>
@@ -4743,28 +4779,28 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ10">
         <v>96</v>
       </c>
       <c r="EK10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EM10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="EO10">
         <v>0</v>
@@ -4784,10 +4820,10 @@
         <v>155</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -4796,7 +4832,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4811,10 +4847,10 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>3648000</v>
+        <v>3296000</v>
       </c>
       <c r="P11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="s">
         <v>162</v>
@@ -4862,13 +4898,13 @@
         <v>1</v>
       </c>
       <c r="AH11">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AJ11">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK11" t="s">
         <v>162</v>
@@ -4895,10 +4931,10 @@
         <v>1</v>
       </c>
       <c r="AS11">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="AT11" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AU11">
         <v>55</v>
@@ -4928,10 +4964,10 @@
         <v>1</v>
       </c>
       <c r="BD11">
-        <v>6300</v>
+        <v>5000</v>
       </c>
       <c r="BE11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="BF11">
         <v>0</v>
@@ -4943,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="BI11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BJ11">
         <v>2</v>
@@ -4952,7 +4988,7 @@
         <v>9</v>
       </c>
       <c r="BL11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BM11">
         <v>0</v>
@@ -4964,17 +5000,17 @@
         <v>1</v>
       </c>
       <c r="BS11" t="s">
+        <v>186</v>
+      </c>
+      <c r="BT11">
+        <v>2</v>
+      </c>
+      <c r="BU11">
+        <v>9</v>
+      </c>
+      <c r="BV11" t="s">
         <v>181</v>
       </c>
-      <c r="BT11">
-        <v>2</v>
-      </c>
-      <c r="BU11">
-        <v>9</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>177</v>
-      </c>
       <c r="BW11">
         <v>0</v>
       </c>
@@ -4985,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="CC11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CD11">
         <v>2</v>
@@ -4994,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="CF11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5006,49 +5042,19 @@
         <v>1</v>
       </c>
       <c r="CL11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO11" t="b">
         <v>1</v>
       </c>
-      <c r="CP11" t="s">
-        <v>187</v>
-      </c>
-      <c r="CQ11">
-        <v>75000</v>
-      </c>
-      <c r="CR11">
-        <v>20000</v>
-      </c>
-      <c r="CS11">
-        <v>7200</v>
-      </c>
-      <c r="CT11">
-        <v>11000</v>
-      </c>
-      <c r="CU11">
-        <v>100000</v>
-      </c>
-      <c r="CV11">
-        <v>0.9</v>
-      </c>
-      <c r="CW11">
-        <v>0.8</v>
-      </c>
-      <c r="CX11" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY11" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK11">
         <v>0.05</v>
@@ -5063,10 +5069,10 @@
         <v>8.5</v>
       </c>
       <c r="DO11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DQ11">
         <v>1</v>
@@ -5075,13 +5081,13 @@
         <v>1</v>
       </c>
       <c r="DS11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT11">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="DU11">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="DV11">
         <v>0.95</v>
@@ -5096,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="DZ11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EA11">
         <v>0</v>
@@ -5105,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EI11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ11">
         <v>96</v>
       </c>
       <c r="EK11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL11">
         <v>36</v>
       </c>
       <c r="EM11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EN11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EO11">
         <v>0</v>
@@ -5162,13 +5168,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -5602,22 +5608,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>420</v>
+        <v>800</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -5626,7 +5632,7 @@
         <v>2.6</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -5641,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>11635000</v>
+        <v>15464000</v>
       </c>
       <c r="T2" t="s">
         <v>162</v>
@@ -5686,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="AK2">
-        <v>23100000</v>
+        <v>120000000</v>
       </c>
       <c r="AN2" t="s">
         <v>162</v>
@@ -5713,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="AV2">
-        <v>12600</v>
+        <v>22000</v>
       </c>
       <c r="AY2" t="s">
         <v>162</v>
@@ -5740,10 +5746,10 @@
         <v>1</v>
       </c>
       <c r="BG2">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="BH2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -5755,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM2">
         <v>2</v>
@@ -5764,59 +5770,50 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="b">
         <v>1</v>
       </c>
-      <c r="BS2">
-        <v>8400</v>
-      </c>
-      <c r="BT2" t="s">
+      <c r="BV2" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW2">
+        <v>2</v>
+      </c>
+      <c r="BX2">
+        <v>9</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>181</v>
+      </c>
+      <c r="BZ2">
+        <v>1</v>
+      </c>
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>3700</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>229</v>
+      </c>
+      <c r="CE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF2" t="s">
         <v>180</v>
       </c>
-      <c r="BU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW2">
-        <v>2</v>
-      </c>
-      <c r="BX2">
-        <v>9</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ2">
-        <v>1</v>
-      </c>
-      <c r="CA2">
-        <v>1</v>
-      </c>
-      <c r="CB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2">
-        <v>1900</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>228</v>
-      </c>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>176</v>
-      </c>
       <c r="CG2">
         <v>2</v>
       </c>
@@ -5824,7 +5821,7 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -5836,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="CO2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -5848,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="DR2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -5863,10 +5860,10 @@
         <v>1</v>
       </c>
       <c r="DW2">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="DX2">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="DY2">
         <v>0.95</v>
@@ -5881,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -5893,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>12000</v>
+        <v>60000</v>
       </c>
       <c r="EH2">
-        <v>23000</v>
+        <v>120000</v>
       </c>
       <c r="EI2">
         <v>0.95</v>
@@ -5905,25 +5902,25 @@
         <v>0.1</v>
       </c>
       <c r="EK2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM2">
         <v>96</v>
       </c>
       <c r="EN2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="EP2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER2">
         <v>0</v>
@@ -5940,22 +5937,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -5964,7 +5961,7 @@
         <v>2.6</v>
       </c>
       <c r="M3">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -5979,10 +5976,10 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>2262000</v>
+        <v>2455000</v>
       </c>
       <c r="S3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="T3" t="s">
         <v>162</v>
@@ -6027,10 +6024,10 @@
         <v>1</v>
       </c>
       <c r="AK3">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL3" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="AM3">
         <v>55</v>
@@ -6063,7 +6060,7 @@
         <v>2400</v>
       </c>
       <c r="AW3" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="AX3">
         <v>55</v>
@@ -6093,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM3">
         <v>2</v>
@@ -6102,7 +6099,7 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP3">
         <v>0</v>
@@ -6114,17 +6111,17 @@
         <v>1</v>
       </c>
       <c r="BV3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW3">
+        <v>2</v>
+      </c>
+      <c r="BX3">
+        <v>9</v>
+      </c>
+      <c r="BY3" t="s">
         <v>181</v>
       </c>
-      <c r="BW3">
-        <v>2</v>
-      </c>
-      <c r="BX3">
-        <v>9</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ3">
         <v>0</v>
       </c>
@@ -6135,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="CF3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG3">
         <v>2</v>
@@ -6144,7 +6141,7 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ3">
         <v>0</v>
@@ -6156,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="CO3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP3">
         <v>0</v>
@@ -6168,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="DM3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="DN3">
         <v>0.05</v>
@@ -6183,10 +6180,10 @@
         <v>8</v>
       </c>
       <c r="DR3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT3">
         <v>0</v>
@@ -6198,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="EC3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED3">
         <v>0</v>
@@ -6210,25 +6207,25 @@
         <v>1</v>
       </c>
       <c r="EK3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM3">
         <v>96</v>
       </c>
       <c r="EN3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO3">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EP3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="ER3">
         <v>0</v>
@@ -6245,22 +6242,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -6269,7 +6266,7 @@
         <v>2.6</v>
       </c>
       <c r="M4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -6284,10 +6281,10 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>1720000</v>
+        <v>2687000</v>
       </c>
       <c r="S4" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="T4" t="s">
         <v>162</v>
@@ -6332,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="AK4">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM4">
         <v>55</v>
@@ -6365,10 +6362,10 @@
         <v>1</v>
       </c>
       <c r="AV4">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="AW4" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="AX4">
         <v>55</v>
@@ -6398,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM4">
         <v>2</v>
@@ -6407,7 +6404,7 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP4">
         <v>0</v>
@@ -6419,17 +6416,17 @@
         <v>1</v>
       </c>
       <c r="BV4" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW4">
+        <v>2</v>
+      </c>
+      <c r="BX4">
+        <v>9</v>
+      </c>
+      <c r="BY4" t="s">
         <v>181</v>
       </c>
-      <c r="BW4">
-        <v>2</v>
-      </c>
-      <c r="BX4">
-        <v>9</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ4">
         <v>0</v>
       </c>
@@ -6440,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="CF4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG4">
         <v>2</v>
@@ -6449,7 +6446,7 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -6461,49 +6458,19 @@
         <v>1</v>
       </c>
       <c r="CO4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="b">
         <v>1</v>
       </c>
-      <c r="CS4" t="s">
-        <v>184</v>
-      </c>
-      <c r="CT4">
-        <v>50000</v>
-      </c>
-      <c r="CU4">
-        <v>15000</v>
-      </c>
-      <c r="CV4">
-        <v>7200</v>
-      </c>
-      <c r="CW4">
-        <v>7200</v>
-      </c>
-      <c r="CX4">
-        <v>50000</v>
-      </c>
-      <c r="CY4">
-        <v>0.9</v>
-      </c>
-      <c r="CZ4">
-        <v>0.8</v>
-      </c>
-      <c r="DA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="b">
-        <v>0</v>
-      </c>
       <c r="DM4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="DN4">
         <v>0.05</v>
@@ -6518,10 +6485,10 @@
         <v>8</v>
       </c>
       <c r="DR4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT4">
         <v>0</v>
@@ -6533,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED4">
         <v>0</v>
@@ -6545,22 +6512,22 @@
         <v>1</v>
       </c>
       <c r="EK4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM4">
         <v>96</v>
       </c>
       <c r="EN4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO4">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -6580,22 +6547,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6604,7 +6571,7 @@
         <v>2.6</v>
       </c>
       <c r="M5">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -6619,10 +6586,10 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>2262000</v>
+        <v>1720000</v>
       </c>
       <c r="S5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="T5" t="s">
         <v>162</v>
@@ -6667,13 +6634,13 @@
         <v>1</v>
       </c>
       <c r="AK5">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AM5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="s">
         <v>162</v>
@@ -6700,10 +6667,10 @@
         <v>1</v>
       </c>
       <c r="AV5">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="AW5" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="AX5">
         <v>55</v>
@@ -6733,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM5">
         <v>2</v>
@@ -6742,7 +6709,7 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP5">
         <v>0</v>
@@ -6754,17 +6721,17 @@
         <v>1</v>
       </c>
       <c r="BV5" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW5">
+        <v>2</v>
+      </c>
+      <c r="BX5">
+        <v>9</v>
+      </c>
+      <c r="BY5" t="s">
         <v>181</v>
       </c>
-      <c r="BW5">
-        <v>2</v>
-      </c>
-      <c r="BX5">
-        <v>9</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ5">
         <v>0</v>
       </c>
@@ -6775,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="CF5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG5">
         <v>2</v>
@@ -6784,7 +6751,7 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ5">
         <v>0</v>
@@ -6796,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="CO5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP5">
         <v>0</v>
@@ -6823,10 +6790,10 @@
         <v>8</v>
       </c>
       <c r="DR5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT5">
         <v>0</v>
@@ -6838,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED5">
         <v>0</v>
@@ -6850,22 +6817,22 @@
         <v>1</v>
       </c>
       <c r="EK5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM5">
         <v>96</v>
       </c>
       <c r="EN5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO5">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ5">
         <v>0</v>
@@ -6885,22 +6852,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -6909,7 +6876,7 @@
         <v>2.6</v>
       </c>
       <c r="M6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -6924,10 +6891,10 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>1158000</v>
+        <v>1266000</v>
       </c>
       <c r="S6" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="T6" t="s">
         <v>162</v>
@@ -6972,13 +6939,13 @@
         <v>1</v>
       </c>
       <c r="AK6">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AM6">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN6" t="s">
         <v>162</v>
@@ -7005,10 +6972,10 @@
         <v>1</v>
       </c>
       <c r="AV6">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="AW6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AX6">
         <v>55</v>
@@ -7038,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM6">
         <v>2</v>
@@ -7047,7 +7014,7 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -7059,17 +7026,17 @@
         <v>1</v>
       </c>
       <c r="BV6" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW6">
+        <v>2</v>
+      </c>
+      <c r="BX6">
+        <v>9</v>
+      </c>
+      <c r="BY6" t="s">
         <v>181</v>
       </c>
-      <c r="BW6">
-        <v>2</v>
-      </c>
-      <c r="BX6">
-        <v>9</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ6">
         <v>0</v>
       </c>
@@ -7080,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="CF6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG6">
         <v>2</v>
@@ -7089,7 +7056,7 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -7101,46 +7068,16 @@
         <v>1</v>
       </c>
       <c r="CO6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR6" t="b">
         <v>1</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT6">
-        <v>75000</v>
-      </c>
-      <c r="CU6">
-        <v>20000</v>
-      </c>
-      <c r="CV6">
-        <v>7200</v>
-      </c>
-      <c r="CW6">
-        <v>11000</v>
-      </c>
-      <c r="CX6">
-        <v>100000</v>
-      </c>
-      <c r="CY6">
-        <v>0.9</v>
-      </c>
-      <c r="CZ6">
-        <v>0.8</v>
-      </c>
-      <c r="DA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="b">
-        <v>0</v>
       </c>
       <c r="DM6" t="s">
         <v>234</v>
@@ -7158,10 +7095,10 @@
         <v>8</v>
       </c>
       <c r="DR6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT6">
         <v>0</v>
@@ -7173,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED6">
         <v>0</v>
@@ -7185,25 +7122,25 @@
         <v>1</v>
       </c>
       <c r="EK6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM6">
         <v>96</v>
       </c>
       <c r="EN6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="EP6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="ER6">
         <v>0</v>
@@ -7220,22 +7157,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -7244,7 +7181,7 @@
         <v>2.6</v>
       </c>
       <c r="M7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -7259,10 +7196,10 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>2687000</v>
+        <v>1266000</v>
       </c>
       <c r="S7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="T7" t="s">
         <v>162</v>
@@ -7307,13 +7244,13 @@
         <v>1</v>
       </c>
       <c r="AK7">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AM7">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN7" t="s">
         <v>162</v>
@@ -7340,10 +7277,10 @@
         <v>1</v>
       </c>
       <c r="AV7">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="AW7" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="AX7">
         <v>55</v>
@@ -7373,7 +7310,7 @@
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM7">
         <v>2</v>
@@ -7382,7 +7319,7 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP7">
         <v>0</v>
@@ -7394,17 +7331,17 @@
         <v>1</v>
       </c>
       <c r="BV7" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW7">
+        <v>2</v>
+      </c>
+      <c r="BX7">
+        <v>9</v>
+      </c>
+      <c r="BY7" t="s">
         <v>181</v>
       </c>
-      <c r="BW7">
-        <v>2</v>
-      </c>
-      <c r="BX7">
-        <v>9</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ7">
         <v>0</v>
       </c>
@@ -7415,7 +7352,7 @@
         <v>1</v>
       </c>
       <c r="CF7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG7">
         <v>2</v>
@@ -7424,7 +7361,7 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ7">
         <v>0</v>
@@ -7436,16 +7373,76 @@
         <v>1</v>
       </c>
       <c r="CO7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR7" t="b">
         <v>1</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>230</v>
+      </c>
+      <c r="CT7">
+        <v>50000</v>
+      </c>
+      <c r="CU7">
+        <v>15000</v>
+      </c>
+      <c r="CV7">
+        <v>7200</v>
+      </c>
+      <c r="CW7">
+        <v>7200</v>
+      </c>
+      <c r="CX7">
+        <v>50000</v>
+      </c>
+      <c r="CY7">
+        <v>0.9</v>
+      </c>
+      <c r="CZ7">
+        <v>0.8</v>
+      </c>
+      <c r="DA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="s">
+        <v>191</v>
+      </c>
+      <c r="DD7">
+        <v>100000</v>
+      </c>
+      <c r="DE7">
+        <v>25000</v>
+      </c>
+      <c r="DF7">
+        <v>11000</v>
+      </c>
+      <c r="DG7">
+        <v>22000</v>
+      </c>
+      <c r="DH7">
+        <v>200000</v>
+      </c>
+      <c r="DI7">
+        <v>0.9</v>
+      </c>
+      <c r="DJ7">
+        <v>0.8</v>
+      </c>
+      <c r="DK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="b">
+        <v>0</v>
       </c>
       <c r="DM7" t="s">
         <v>235</v>
@@ -7463,10 +7460,10 @@
         <v>8</v>
       </c>
       <c r="DR7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT7">
         <v>0</v>
@@ -7478,7 +7475,7 @@
         <v>1</v>
       </c>
       <c r="EC7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED7">
         <v>0</v>
@@ -7490,25 +7487,25 @@
         <v>1</v>
       </c>
       <c r="EK7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM7">
         <v>96</v>
       </c>
       <c r="EN7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO7">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="EP7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER7">
         <v>0</v>
@@ -7525,22 +7522,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7549,7 +7546,7 @@
         <v>2.6</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -7567,7 +7564,7 @@
         <v>1546000</v>
       </c>
       <c r="S8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="T8" t="s">
         <v>162</v>
@@ -7612,13 +7609,13 @@
         <v>1</v>
       </c>
       <c r="AK8">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN8" t="s">
         <v>162</v>
@@ -7645,10 +7642,10 @@
         <v>1</v>
       </c>
       <c r="AV8">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="AW8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AX8">
         <v>55</v>
@@ -7678,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM8">
         <v>2</v>
@@ -7687,7 +7684,7 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP8">
         <v>0</v>
@@ -7699,17 +7696,17 @@
         <v>1</v>
       </c>
       <c r="BV8" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW8">
+        <v>2</v>
+      </c>
+      <c r="BX8">
+        <v>9</v>
+      </c>
+      <c r="BY8" t="s">
         <v>181</v>
       </c>
-      <c r="BW8">
-        <v>2</v>
-      </c>
-      <c r="BX8">
-        <v>9</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ8">
         <v>0</v>
       </c>
@@ -7720,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="CF8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG8">
         <v>2</v>
@@ -7729,7 +7726,7 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -7741,7 +7738,7 @@
         <v>1</v>
       </c>
       <c r="CO8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP8">
         <v>0</v>
@@ -7753,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="DM8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="DN8">
         <v>0.05</v>
@@ -7768,10 +7765,10 @@
         <v>8</v>
       </c>
       <c r="DR8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT8">
         <v>0</v>
@@ -7783,7 +7780,7 @@
         <v>1</v>
       </c>
       <c r="EC8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED8">
         <v>0</v>
@@ -7795,25 +7792,25 @@
         <v>1</v>
       </c>
       <c r="EK8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM8">
         <v>96</v>
       </c>
       <c r="EN8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO8">
         <v>36</v>
       </c>
       <c r="EP8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="ER8">
         <v>0</v>
@@ -7830,10 +7827,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -7845,7 +7842,7 @@
         <v>4</v>
       </c>
       <c r="J9">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7860,16 +7857,19 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>14531000</v>
+        <v>2262000</v>
+      </c>
+      <c r="S9" t="s">
+        <v>221</v>
       </c>
       <c r="T9" t="s">
         <v>162</v>
@@ -7905,16 +7905,22 @@
         <v>163</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9">
-        <v>120000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM9">
+        <v>55</v>
       </c>
       <c r="AN9" t="s">
         <v>162</v>
@@ -7932,16 +7938,22 @@
         <v>90</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="b">
         <v>1</v>
       </c>
       <c r="AV9">
-        <v>22400</v>
+        <v>2400</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AX9">
+        <v>55</v>
       </c>
       <c r="AY9" t="s">
         <v>162</v>
@@ -7959,31 +7971,16 @@
         <v>90</v>
       </c>
       <c r="BD9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="b">
         <v>1</v>
       </c>
-      <c r="BG9">
-        <v>21000</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>227</v>
-      </c>
-      <c r="BI9">
-        <v>0</v>
-      </c>
-      <c r="BJ9">
-        <v>40</v>
-      </c>
-      <c r="BK9" t="b">
-        <v>1</v>
-      </c>
       <c r="BL9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM9">
         <v>2</v>
@@ -7992,7 +7989,7 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP9">
         <v>0</v>
@@ -8004,37 +8001,28 @@
         <v>1</v>
       </c>
       <c r="BV9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW9">
+        <v>2</v>
+      </c>
+      <c r="BX9">
+        <v>9</v>
+      </c>
+      <c r="BY9" t="s">
         <v>181</v>
       </c>
-      <c r="BW9">
-        <v>2</v>
-      </c>
-      <c r="BX9">
-        <v>9</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="b">
         <v>1</v>
       </c>
-      <c r="CC9">
-        <v>1600</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>228</v>
-      </c>
-      <c r="CE9" t="b">
-        <v>0</v>
-      </c>
       <c r="CF9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG9">
         <v>2</v>
@@ -8043,7 +8031,7 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ9">
         <v>0</v>
@@ -8055,91 +8043,106 @@
         <v>1</v>
       </c>
       <c r="CO9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR9" t="b">
         <v>1</v>
       </c>
+      <c r="CS9" t="s">
+        <v>231</v>
+      </c>
+      <c r="CT9">
+        <v>75000</v>
+      </c>
+      <c r="CU9">
+        <v>20000</v>
+      </c>
+      <c r="CV9">
+        <v>7200</v>
+      </c>
+      <c r="CW9">
+        <v>11000</v>
+      </c>
+      <c r="CX9">
+        <v>100000</v>
+      </c>
+      <c r="CY9">
+        <v>0.9</v>
+      </c>
+      <c r="CZ9">
+        <v>0.8</v>
+      </c>
+      <c r="DA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="s">
+        <v>234</v>
+      </c>
+      <c r="DN9">
+        <v>0.05</v>
+      </c>
+      <c r="DO9">
+        <v>0.5</v>
+      </c>
+      <c r="DP9">
+        <v>0.8</v>
+      </c>
+      <c r="DQ9">
+        <v>8</v>
+      </c>
       <c r="DR9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
-      <c r="DW9">
-        <v>15000</v>
-      </c>
-      <c r="DX9">
-        <v>15000</v>
-      </c>
-      <c r="DY9">
-        <v>0.95</v>
-      </c>
-      <c r="DZ9">
-        <v>0.1</v>
-      </c>
-      <c r="EA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB9" t="b">
-        <v>0</v>
-      </c>
       <c r="EC9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="b">
         <v>1</v>
       </c>
-      <c r="EG9">
-        <v>60000</v>
-      </c>
-      <c r="EH9">
-        <v>120000</v>
-      </c>
-      <c r="EI9">
-        <v>0.95</v>
-      </c>
-      <c r="EJ9">
-        <v>0.1</v>
-      </c>
       <c r="EK9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM9">
         <v>96</v>
       </c>
       <c r="EN9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO9">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="EP9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -8159,10 +8162,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8198,10 +8201,10 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>2455000</v>
+        <v>2262000</v>
       </c>
       <c r="S10" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="T10" t="s">
         <v>162</v>
@@ -8279,10 +8282,10 @@
         <v>1</v>
       </c>
       <c r="AV10">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW10" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="AX10">
         <v>55</v>
@@ -8312,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM10">
         <v>2</v>
@@ -8321,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP10">
         <v>0</v>
@@ -8333,17 +8336,17 @@
         <v>1</v>
       </c>
       <c r="BV10" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW10">
+        <v>2</v>
+      </c>
+      <c r="BX10">
+        <v>9</v>
+      </c>
+      <c r="BY10" t="s">
         <v>181</v>
       </c>
-      <c r="BW10">
-        <v>2</v>
-      </c>
-      <c r="BX10">
-        <v>9</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ10">
         <v>0</v>
       </c>
@@ -8354,7 +8357,7 @@
         <v>1</v>
       </c>
       <c r="CF10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG10">
         <v>2</v>
@@ -8363,7 +8366,7 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ10">
         <v>0</v>
@@ -8375,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="CO10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP10">
         <v>0</v>
@@ -8387,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="DM10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="DN10">
         <v>0.05</v>
@@ -8402,10 +8405,10 @@
         <v>8</v>
       </c>
       <c r="DR10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -8417,7 +8420,7 @@
         <v>1</v>
       </c>
       <c r="EC10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED10">
         <v>0</v>
@@ -8429,25 +8432,25 @@
         <v>1</v>
       </c>
       <c r="EK10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM10">
         <v>96</v>
       </c>
       <c r="EN10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="EP10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="ER10">
         <v>0</v>
@@ -8464,22 +8467,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>420</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -8488,25 +8491,22 @@
         <v>2.6</v>
       </c>
       <c r="M11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1546000</v>
-      </c>
-      <c r="S11" t="s">
-        <v>217</v>
+        <v>11172000</v>
       </c>
       <c r="T11" t="s">
         <v>162</v>
@@ -8542,22 +8542,16 @@
         <v>163</v>
       </c>
       <c r="AH11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11">
-        <v>15000000</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM11">
-        <v>35</v>
+        <v>23100000</v>
       </c>
       <c r="AN11" t="s">
         <v>162</v>
@@ -8575,22 +8569,16 @@
         <v>90</v>
       </c>
       <c r="AS11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="b">
         <v>1</v>
       </c>
       <c r="AV11">
-        <v>3200</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>224</v>
-      </c>
-      <c r="AX11">
-        <v>55</v>
+        <v>12600</v>
       </c>
       <c r="AY11" t="s">
         <v>162</v>
@@ -8608,16 +8596,31 @@
         <v>90</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF11" t="b">
         <v>1</v>
       </c>
+      <c r="BG11">
+        <v>17000</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>228</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>40</v>
+      </c>
+      <c r="BK11" t="b">
+        <v>1</v>
+      </c>
       <c r="BL11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM11">
         <v>2</v>
@@ -8626,40 +8629,58 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR11" t="b">
         <v>1</v>
       </c>
+      <c r="BS11">
+        <v>6700</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>182</v>
+      </c>
+      <c r="BU11" t="b">
+        <v>1</v>
+      </c>
       <c r="BV11" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW11">
+        <v>2</v>
+      </c>
+      <c r="BX11">
+        <v>9</v>
+      </c>
+      <c r="BY11" t="s">
         <v>181</v>
       </c>
-      <c r="BW11">
-        <v>2</v>
-      </c>
-      <c r="BX11">
-        <v>9</v>
-      </c>
-      <c r="BY11" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB11" t="b">
         <v>1</v>
       </c>
+      <c r="CC11">
+        <v>1200</v>
+      </c>
+      <c r="CD11" t="s">
+        <v>229</v>
+      </c>
+      <c r="CE11" t="b">
+        <v>0</v>
+      </c>
       <c r="CF11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG11">
         <v>2</v>
@@ -8668,7 +8689,7 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ11">
         <v>0</v>
@@ -8680,106 +8701,91 @@
         <v>1</v>
       </c>
       <c r="CO11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR11" t="b">
         <v>1</v>
       </c>
-      <c r="CS11" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT11">
-        <v>50000</v>
-      </c>
-      <c r="CU11">
-        <v>15000</v>
-      </c>
-      <c r="CV11">
-        <v>7200</v>
-      </c>
-      <c r="CW11">
-        <v>7200</v>
-      </c>
-      <c r="CX11">
-        <v>50000</v>
-      </c>
-      <c r="CY11">
-        <v>0.9</v>
-      </c>
-      <c r="CZ11">
-        <v>0.8</v>
-      </c>
-      <c r="DA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM11" t="s">
-        <v>235</v>
-      </c>
-      <c r="DN11">
-        <v>0.05</v>
-      </c>
-      <c r="DO11">
-        <v>0.5</v>
-      </c>
-      <c r="DP11">
-        <v>0.8</v>
-      </c>
-      <c r="DQ11">
-        <v>8</v>
-      </c>
       <c r="DR11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV11" t="b">
         <v>1</v>
       </c>
+      <c r="DW11">
+        <v>11000</v>
+      </c>
+      <c r="DX11">
+        <v>11000</v>
+      </c>
+      <c r="DY11">
+        <v>0.95</v>
+      </c>
+      <c r="DZ11">
+        <v>0.1</v>
+      </c>
+      <c r="EA11" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB11" t="b">
+        <v>0</v>
+      </c>
       <c r="EC11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF11" t="b">
         <v>1</v>
       </c>
+      <c r="EG11">
+        <v>12000</v>
+      </c>
+      <c r="EH11">
+        <v>23000</v>
+      </c>
+      <c r="EI11">
+        <v>0.95</v>
+      </c>
+      <c r="EJ11">
+        <v>0.1</v>
+      </c>
       <c r="EK11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM11">
         <v>96</v>
       </c>
       <c r="EN11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="EP11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ11">
         <v>30</v>
@@ -8799,22 +8805,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -8823,7 +8829,7 @@
         <v>2.6</v>
       </c>
       <c r="M12">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -8838,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2012000</v>
+        <v>1720000</v>
       </c>
       <c r="S12" t="s">
         <v>218</v>
@@ -8886,10 +8892,10 @@
         <v>1</v>
       </c>
       <c r="AK12">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL12" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="AM12">
         <v>55</v>
@@ -8922,7 +8928,7 @@
         <v>2400</v>
       </c>
       <c r="AW12" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="AX12">
         <v>55</v>
@@ -8952,7 +8958,7 @@
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM12">
         <v>2</v>
@@ -8961,7 +8967,7 @@
         <v>9</v>
       </c>
       <c r="BO12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP12">
         <v>0</v>
@@ -8973,17 +8979,17 @@
         <v>1</v>
       </c>
       <c r="BV12" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW12">
+        <v>2</v>
+      </c>
+      <c r="BX12">
+        <v>9</v>
+      </c>
+      <c r="BY12" t="s">
         <v>181</v>
       </c>
-      <c r="BW12">
-        <v>2</v>
-      </c>
-      <c r="BX12">
-        <v>9</v>
-      </c>
-      <c r="BY12" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ12">
         <v>0</v>
       </c>
@@ -8994,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="CF12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG12">
         <v>2</v>
@@ -9003,7 +9009,7 @@
         <v>9</v>
       </c>
       <c r="CI12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ12">
         <v>0</v>
@@ -9015,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="CO12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP12">
         <v>0</v>
@@ -9027,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="DM12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="DN12">
         <v>0.05</v>
@@ -9042,10 +9048,10 @@
         <v>8</v>
       </c>
       <c r="DR12" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT12">
         <v>0</v>
@@ -9057,7 +9063,7 @@
         <v>1</v>
       </c>
       <c r="EC12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED12">
         <v>0</v>
@@ -9069,25 +9075,25 @@
         <v>1</v>
       </c>
       <c r="EK12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM12">
         <v>96</v>
       </c>
       <c r="EN12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO12">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="ER12">
         <v>0</v>
@@ -9104,22 +9110,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -9128,7 +9134,7 @@
         <v>2.6</v>
       </c>
       <c r="M13">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -9143,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2896000</v>
+        <v>2455000</v>
       </c>
       <c r="S13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T13" t="s">
         <v>162</v>
@@ -9191,10 +9197,10 @@
         <v>1</v>
       </c>
       <c r="AK13">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AM13">
         <v>55</v>
@@ -9224,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="AV13">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="AW13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AX13">
         <v>55</v>
@@ -9257,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM13">
         <v>2</v>
@@ -9266,7 +9272,7 @@
         <v>9</v>
       </c>
       <c r="BO13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP13">
         <v>0</v>
@@ -9278,17 +9284,17 @@
         <v>1</v>
       </c>
       <c r="BV13" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW13">
+        <v>2</v>
+      </c>
+      <c r="BX13">
+        <v>9</v>
+      </c>
+      <c r="BY13" t="s">
         <v>181</v>
       </c>
-      <c r="BW13">
-        <v>2</v>
-      </c>
-      <c r="BX13">
-        <v>9</v>
-      </c>
-      <c r="BY13" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ13">
         <v>0</v>
       </c>
@@ -9299,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="CF13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG13">
         <v>2</v>
@@ -9308,7 +9314,7 @@
         <v>9</v>
       </c>
       <c r="CI13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ13">
         <v>0</v>
@@ -9320,16 +9326,46 @@
         <v>1</v>
       </c>
       <c r="CO13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR13" t="b">
         <v>1</v>
+      </c>
+      <c r="CS13" t="s">
+        <v>232</v>
+      </c>
+      <c r="CT13">
+        <v>75000</v>
+      </c>
+      <c r="CU13">
+        <v>20000</v>
+      </c>
+      <c r="CV13">
+        <v>7200</v>
+      </c>
+      <c r="CW13">
+        <v>11000</v>
+      </c>
+      <c r="CX13">
+        <v>100000</v>
+      </c>
+      <c r="CY13">
+        <v>0.9</v>
+      </c>
+      <c r="CZ13">
+        <v>0.8</v>
+      </c>
+      <c r="DA13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="b">
+        <v>0</v>
       </c>
       <c r="DM13" t="s">
         <v>237</v>
@@ -9347,10 +9383,10 @@
         <v>8</v>
       </c>
       <c r="DR13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT13">
         <v>0</v>
@@ -9362,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="EC13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED13">
         <v>0</v>
@@ -9374,22 +9410,22 @@
         <v>1</v>
       </c>
       <c r="EK13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM13">
         <v>96</v>
       </c>
       <c r="EN13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO13">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ13">
         <v>0</v>
@@ -9409,22 +9445,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -9433,7 +9469,7 @@
         <v>2.6</v>
       </c>
       <c r="M14">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -9448,7 +9484,7 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>945000</v>
+        <v>1546000</v>
       </c>
       <c r="S14" t="s">
         <v>220</v>
@@ -9496,13 +9532,13 @@
         <v>1</v>
       </c>
       <c r="AK14">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL14" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="AM14">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="s">
         <v>162</v>
@@ -9529,10 +9565,10 @@
         <v>1</v>
       </c>
       <c r="AV14">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="AW14" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="AX14">
         <v>55</v>
@@ -9562,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM14">
         <v>2</v>
@@ -9571,7 +9607,7 @@
         <v>9</v>
       </c>
       <c r="BO14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP14">
         <v>0</v>
@@ -9583,17 +9619,17 @@
         <v>1</v>
       </c>
       <c r="BV14" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW14">
+        <v>2</v>
+      </c>
+      <c r="BX14">
+        <v>9</v>
+      </c>
+      <c r="BY14" t="s">
         <v>181</v>
       </c>
-      <c r="BW14">
-        <v>2</v>
-      </c>
-      <c r="BX14">
-        <v>9</v>
-      </c>
-      <c r="BY14" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ14">
         <v>0</v>
       </c>
@@ -9604,7 +9640,7 @@
         <v>1</v>
       </c>
       <c r="CF14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG14">
         <v>2</v>
@@ -9613,7 +9649,7 @@
         <v>9</v>
       </c>
       <c r="CI14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ14">
         <v>0</v>
@@ -9625,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="CO14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP14">
         <v>0</v>
@@ -9637,7 +9673,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="DN14">
         <v>0.05</v>
@@ -9652,10 +9688,10 @@
         <v>8</v>
       </c>
       <c r="DR14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT14">
         <v>0</v>
@@ -9667,7 +9703,7 @@
         <v>1</v>
       </c>
       <c r="EC14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED14">
         <v>0</v>
@@ -9679,25 +9715,25 @@
         <v>1</v>
       </c>
       <c r="EK14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM14">
         <v>96</v>
       </c>
       <c r="EN14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO14">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="EP14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="ER14">
         <v>0</v>
@@ -9714,22 +9750,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -9738,7 +9774,7 @@
         <v>2.6</v>
       </c>
       <c r="M15">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -9753,7 +9789,7 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>945000</v>
+        <v>1546000</v>
       </c>
       <c r="S15" t="s">
         <v>220</v>
@@ -9801,13 +9837,13 @@
         <v>1</v>
       </c>
       <c r="AK15">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL15" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="AM15">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN15" t="s">
         <v>162</v>
@@ -9834,10 +9870,10 @@
         <v>1</v>
       </c>
       <c r="AV15">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="AW15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AX15">
         <v>55</v>
@@ -9867,7 +9903,7 @@
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM15">
         <v>2</v>
@@ -9876,7 +9912,7 @@
         <v>9</v>
       </c>
       <c r="BO15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP15">
         <v>0</v>
@@ -9888,17 +9924,17 @@
         <v>1</v>
       </c>
       <c r="BV15" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW15">
+        <v>2</v>
+      </c>
+      <c r="BX15">
+        <v>9</v>
+      </c>
+      <c r="BY15" t="s">
         <v>181</v>
       </c>
-      <c r="BW15">
-        <v>2</v>
-      </c>
-      <c r="BX15">
-        <v>9</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ15">
         <v>0</v>
       </c>
@@ -9909,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="CF15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG15">
         <v>2</v>
@@ -9918,7 +9954,7 @@
         <v>9</v>
       </c>
       <c r="CI15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ15">
         <v>0</v>
@@ -9930,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="CO15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP15">
         <v>0</v>
@@ -9942,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="DM15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="DN15">
         <v>0.05</v>
@@ -9957,10 +9993,10 @@
         <v>8</v>
       </c>
       <c r="DR15" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT15">
         <v>0</v>
@@ -9972,7 +10008,7 @@
         <v>1</v>
       </c>
       <c r="EC15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED15">
         <v>0</v>
@@ -9984,22 +10020,22 @@
         <v>1</v>
       </c>
       <c r="EK15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL15" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM15">
         <v>96</v>
       </c>
       <c r="EN15" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO15">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="EP15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ15">
         <v>20</v>
@@ -10019,22 +10055,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -10043,7 +10079,7 @@
         <v>2.6</v>
       </c>
       <c r="M16">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -10058,10 +10094,10 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>2012000</v>
+        <v>2896000</v>
       </c>
       <c r="S16" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="T16" t="s">
         <v>162</v>
@@ -10106,10 +10142,10 @@
         <v>1</v>
       </c>
       <c r="AK16">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL16" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -10139,10 +10175,10 @@
         <v>1</v>
       </c>
       <c r="AV16">
-        <v>3200</v>
+        <v>2100</v>
       </c>
       <c r="AW16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AX16">
         <v>55</v>
@@ -10172,7 +10208,7 @@
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM16">
         <v>2</v>
@@ -10181,7 +10217,7 @@
         <v>9</v>
       </c>
       <c r="BO16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP16">
         <v>0</v>
@@ -10193,17 +10229,17 @@
         <v>1</v>
       </c>
       <c r="BV16" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW16">
+        <v>2</v>
+      </c>
+      <c r="BX16">
+        <v>9</v>
+      </c>
+      <c r="BY16" t="s">
         <v>181</v>
       </c>
-      <c r="BW16">
-        <v>2</v>
-      </c>
-      <c r="BX16">
-        <v>9</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ16">
         <v>0</v>
       </c>
@@ -10214,7 +10250,7 @@
         <v>1</v>
       </c>
       <c r="CF16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG16">
         <v>2</v>
@@ -10223,7 +10259,7 @@
         <v>9</v>
       </c>
       <c r="CI16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ16">
         <v>0</v>
@@ -10235,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="CO16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP16">
         <v>0</v>
@@ -10247,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="DM16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="DN16">
         <v>0.05</v>
@@ -10262,10 +10298,10 @@
         <v>8</v>
       </c>
       <c r="DR16" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT16">
         <v>0</v>
@@ -10277,7 +10313,7 @@
         <v>1</v>
       </c>
       <c r="EC16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED16">
         <v>0</v>
@@ -10289,25 +10325,25 @@
         <v>1</v>
       </c>
       <c r="EK16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM16">
         <v>96</v>
       </c>
       <c r="EN16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO16">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER16">
         <v>0</v>
@@ -10324,22 +10360,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -10348,7 +10384,7 @@
         <v>2.6</v>
       </c>
       <c r="M17">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -10363,10 +10399,10 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1720000</v>
+        <v>1009000</v>
       </c>
       <c r="S17" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="T17" t="s">
         <v>162</v>
@@ -10411,10 +10447,10 @@
         <v>1</v>
       </c>
       <c r="AK17">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL17" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="AM17">
         <v>35</v>
@@ -10444,10 +10480,10 @@
         <v>1</v>
       </c>
       <c r="AV17">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW17" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="AX17">
         <v>55</v>
@@ -10477,7 +10513,7 @@
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BM17">
         <v>2</v>
@@ -10486,7 +10522,7 @@
         <v>9</v>
       </c>
       <c r="BO17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BP17">
         <v>0</v>
@@ -10498,17 +10534,17 @@
         <v>1</v>
       </c>
       <c r="BV17" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW17">
+        <v>2</v>
+      </c>
+      <c r="BX17">
+        <v>9</v>
+      </c>
+      <c r="BY17" t="s">
         <v>181</v>
       </c>
-      <c r="BW17">
-        <v>2</v>
-      </c>
-      <c r="BX17">
-        <v>9</v>
-      </c>
-      <c r="BY17" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ17">
         <v>0</v>
       </c>
@@ -10519,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="CF17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CG17">
         <v>2</v>
@@ -10528,7 +10564,7 @@
         <v>9</v>
       </c>
       <c r="CI17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CJ17">
         <v>0</v>
@@ -10540,79 +10576,19 @@
         <v>1</v>
       </c>
       <c r="CO17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CP17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CR17" t="b">
         <v>1</v>
       </c>
-      <c r="CS17" t="s">
-        <v>185</v>
-      </c>
-      <c r="CT17">
-        <v>75000</v>
-      </c>
-      <c r="CU17">
-        <v>20000</v>
-      </c>
-      <c r="CV17">
-        <v>7200</v>
-      </c>
-      <c r="CW17">
-        <v>11000</v>
-      </c>
-      <c r="CX17">
-        <v>100000</v>
-      </c>
-      <c r="CY17">
-        <v>0.9</v>
-      </c>
-      <c r="CZ17">
-        <v>0.8</v>
-      </c>
-      <c r="DA17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC17" t="s">
-        <v>230</v>
-      </c>
-      <c r="DD17">
-        <v>50000</v>
-      </c>
-      <c r="DE17">
-        <v>15000</v>
-      </c>
-      <c r="DF17">
-        <v>7200</v>
-      </c>
-      <c r="DG17">
-        <v>7200</v>
-      </c>
-      <c r="DH17">
-        <v>50000</v>
-      </c>
-      <c r="DI17">
-        <v>0.9</v>
-      </c>
-      <c r="DJ17">
-        <v>0.8</v>
-      </c>
-      <c r="DK17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL17" t="b">
-        <v>0</v>
-      </c>
       <c r="DM17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="DN17">
         <v>0.05</v>
@@ -10627,10 +10603,10 @@
         <v>8</v>
       </c>
       <c r="DR17" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="DT17">
         <v>0</v>
@@ -10642,7 +10618,7 @@
         <v>1</v>
       </c>
       <c r="EC17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="ED17">
         <v>0</v>
@@ -10654,25 +10630,25 @@
         <v>1</v>
       </c>
       <c r="EK17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="EL17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM17">
         <v>96</v>
       </c>
       <c r="EN17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO17">
         <v>60</v>
       </c>
       <c r="EP17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="EQ17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER17">
         <v>0</v>
@@ -10708,13 +10684,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -10995,13 +10971,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G2">
-        <v>543</v>
+        <v>182</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -11019,10 +10995,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>15120000</v>
+        <v>7480000</v>
       </c>
       <c r="N2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -11046,7 +11022,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -11061,31 +11037,16 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
-      <c r="AF2">
-        <v>8630000</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>40</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>1</v>
-      </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -11094,7 +11055,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -11106,17 +11067,17 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="s">
         <v>181</v>
       </c>
-      <c r="AV2">
-        <v>2</v>
-      </c>
-      <c r="AW2">
-        <v>9</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>177</v>
-      </c>
       <c r="AY2">
         <v>0</v>
       </c>
@@ -11127,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -11136,7 +11097,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -11148,58 +11109,40 @@
         <v>1</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF2">
-        <v>15100</v>
-      </c>
-      <c r="CG2">
-        <v>15000</v>
-      </c>
-      <c r="CH2">
-        <v>0.95</v>
-      </c>
-      <c r="CI2">
-        <v>0.1</v>
-      </c>
-      <c r="CJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK2" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN2">
         <v>96</v>
       </c>
       <c r="CO2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="CQ2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="CR2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CS2">
         <v>0</v>
@@ -11216,13 +11159,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
         <v>245</v>
       </c>
       <c r="G3">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -11240,7 +11183,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>6850000</v>
+        <v>7320000</v>
       </c>
       <c r="N3" t="s">
         <v>247</v>
@@ -11291,10 +11234,10 @@
         <v>1</v>
       </c>
       <c r="AF3">
-        <v>3260000</v>
+        <v>3300000</v>
       </c>
       <c r="AG3" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AH3">
         <v>-20</v>
@@ -11306,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -11315,7 +11258,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -11327,17 +11270,17 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3" t="s">
         <v>181</v>
       </c>
-      <c r="AV3">
-        <v>2</v>
-      </c>
-      <c r="AW3">
-        <v>9</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>177</v>
-      </c>
       <c r="AY3">
         <v>0</v>
       </c>
@@ -11348,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -11357,7 +11300,7 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI3">
         <v>1</v>
@@ -11369,7 +11312,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>183</v>
+        <v>249</v>
       </c>
       <c r="BM3">
         <v>75000</v>
@@ -11399,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="BV3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="BW3">
         <v>0.05</v>
@@ -11414,10 +11357,10 @@
         <v>8</v>
       </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CC3">
         <v>1</v>
@@ -11426,13 +11369,13 @@
         <v>1</v>
       </c>
       <c r="CE3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CF3">
-        <v>6800</v>
+        <v>7300</v>
       </c>
       <c r="CG3">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="CH3">
         <v>0.95</v>
@@ -11447,25 +11390,25 @@
         <v>0</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN3">
         <v>96</v>
       </c>
       <c r="CO3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="CQ3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="CR3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CS3">
         <v>0</v>
@@ -11482,13 +11425,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G4">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="H4">
         <v>96</v>
@@ -11506,10 +11449,10 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>15360000</v>
+        <v>13990000</v>
       </c>
       <c r="N4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O4" t="s">
         <v>162</v>
@@ -11533,7 +11476,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Y4" t="s">
         <v>162</v>
@@ -11548,16 +11491,31 @@
         <v>163</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
       </c>
+      <c r="AF4">
+        <v>5810000</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>40</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>1</v>
+      </c>
       <c r="AK4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL4">
         <v>2</v>
@@ -11566,7 +11524,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -11578,17 +11536,17 @@
         <v>1</v>
       </c>
       <c r="AU4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV4">
+        <v>2</v>
+      </c>
+      <c r="AW4">
+        <v>9</v>
+      </c>
+      <c r="AX4" t="s">
         <v>181</v>
       </c>
-      <c r="AV4">
-        <v>2</v>
-      </c>
-      <c r="AW4">
-        <v>9</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>177</v>
-      </c>
       <c r="AY4">
         <v>0</v>
       </c>
@@ -11599,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="BE4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF4">
         <v>2</v>
@@ -11608,7 +11566,7 @@
         <v>9</v>
       </c>
       <c r="BH4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI4">
         <v>0</v>
@@ -11620,40 +11578,58 @@
         <v>1</v>
       </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE4" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+      <c r="CF4">
+        <v>14000</v>
+      </c>
+      <c r="CG4">
+        <v>14000</v>
+      </c>
+      <c r="CH4">
+        <v>0.95</v>
+      </c>
+      <c r="CI4">
+        <v>0.1</v>
+      </c>
+      <c r="CJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="b">
+        <v>0</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN4">
         <v>96</v>
       </c>
       <c r="CO4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP4">
         <v>12</v>
       </c>
       <c r="CQ4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="CR4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="CS4">
         <v>0</v>
@@ -11670,13 +11646,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G5">
-        <v>192</v>
+        <v>522</v>
       </c>
       <c r="H5">
         <v>96</v>
@@ -11694,10 +11670,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>7730000</v>
+        <v>15930000</v>
       </c>
       <c r="N5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O5" t="s">
         <v>162</v>
@@ -11721,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="W5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y5" t="s">
         <v>162</v>
@@ -11736,31 +11712,16 @@
         <v>163</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
-      <c r="AF5">
-        <v>4380000</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>226</v>
-      </c>
-      <c r="AH5">
-        <v>-20</v>
-      </c>
-      <c r="AI5">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
-      </c>
       <c r="AK5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL5">
         <v>2</v>
@@ -11769,7 +11730,7 @@
         <v>9</v>
       </c>
       <c r="AN5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -11781,17 +11742,17 @@
         <v>1</v>
       </c>
       <c r="AU5" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5">
+        <v>9</v>
+      </c>
+      <c r="AX5" t="s">
         <v>181</v>
       </c>
-      <c r="AV5">
-        <v>2</v>
-      </c>
-      <c r="AW5">
-        <v>9</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>177</v>
-      </c>
       <c r="AY5">
         <v>0</v>
       </c>
@@ -11802,7 +11763,7 @@
         <v>1</v>
       </c>
       <c r="BE5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF5">
         <v>2</v>
@@ -11811,70 +11772,97 @@
         <v>9</v>
       </c>
       <c r="BH5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="b">
         <v>1</v>
       </c>
+      <c r="BL5" t="s">
+        <v>250</v>
+      </c>
+      <c r="BM5">
+        <v>50000</v>
+      </c>
+      <c r="BN5">
+        <v>20000</v>
+      </c>
+      <c r="BO5">
+        <v>7200</v>
+      </c>
+      <c r="BP5">
+        <v>11000</v>
+      </c>
+      <c r="BQ5">
+        <v>100000</v>
+      </c>
+      <c r="BR5">
+        <v>0.9</v>
+      </c>
+      <c r="BS5">
+        <v>0.8</v>
+      </c>
+      <c r="BT5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW5">
+        <v>0.05</v>
+      </c>
+      <c r="BX5">
+        <v>0.5</v>
+      </c>
+      <c r="BY5">
+        <v>0.8</v>
+      </c>
+      <c r="BZ5">
+        <v>8</v>
+      </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF5">
-        <v>7700</v>
-      </c>
-      <c r="CG5">
-        <v>15000</v>
-      </c>
-      <c r="CH5">
-        <v>0.95</v>
-      </c>
-      <c r="CI5">
-        <v>0.1</v>
-      </c>
-      <c r="CJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN5">
         <v>96</v>
       </c>
       <c r="CO5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP5">
         <v>36</v>
       </c>
       <c r="CQ5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="CR5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CS5">
         <v>0</v>
@@ -11910,13 +11898,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -12227,13 +12215,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G2">
-        <v>2135</v>
+        <v>1714</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -12251,10 +12239,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1002000000</v>
+        <v>604400000</v>
       </c>
       <c r="N2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -12278,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -12293,31 +12281,16 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
-      <c r="AF2">
-        <v>1229000000</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH2">
-        <v>-20</v>
-      </c>
-      <c r="AI2">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>1</v>
-      </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -12326,38 +12299,29 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="b">
         <v>1</v>
       </c>
-      <c r="AR2">
-        <v>104300000</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AT2" t="b">
-        <v>1</v>
-      </c>
       <c r="AU2" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="s">
         <v>181</v>
       </c>
-      <c r="AV2">
-        <v>2</v>
-      </c>
-      <c r="AW2">
-        <v>9</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>177</v>
-      </c>
       <c r="AY2">
         <v>0</v>
       </c>
@@ -12368,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -12377,97 +12341,22 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="b">
         <v>1</v>
       </c>
-      <c r="BL2" t="s">
-        <v>229</v>
-      </c>
-      <c r="BM2">
-        <v>750000</v>
-      </c>
-      <c r="BN2">
-        <v>25000</v>
-      </c>
-      <c r="BO2">
-        <v>11000</v>
-      </c>
-      <c r="BP2">
-        <v>22000</v>
-      </c>
-      <c r="BQ2">
-        <v>200000</v>
-      </c>
-      <c r="BR2">
-        <v>0.9</v>
-      </c>
-      <c r="BS2">
-        <v>0.8</v>
-      </c>
-      <c r="BT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>186</v>
-      </c>
-      <c r="BW2">
-        <v>750000</v>
-      </c>
-      <c r="BX2">
-        <v>25000</v>
-      </c>
-      <c r="BY2">
-        <v>11000</v>
-      </c>
-      <c r="BZ2">
-        <v>22000</v>
-      </c>
-      <c r="CA2">
-        <v>200000</v>
-      </c>
-      <c r="CB2">
-        <v>0.9</v>
-      </c>
-      <c r="CC2">
-        <v>0.8</v>
-      </c>
-      <c r="CD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>188</v>
-      </c>
-      <c r="CG2">
-        <v>0.05</v>
-      </c>
-      <c r="CH2">
-        <v>0.5</v>
-      </c>
-      <c r="CI2">
-        <v>0.8</v>
-      </c>
-      <c r="CJ2">
-        <v>8</v>
-      </c>
       <c r="CK2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -12476,25 +12365,25 @@
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CV2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CW2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CX2">
         <v>96</v>
       </c>
       <c r="CY2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CZ2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="DA2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="DB2">
         <v>30</v>
@@ -12514,13 +12403,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G3">
-        <v>4819</v>
+        <v>4924</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -12538,10 +12427,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1211000000</v>
+        <v>1140500000</v>
       </c>
       <c r="N3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -12565,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -12589,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -12598,7 +12487,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -12610,17 +12499,17 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3" t="s">
         <v>181</v>
       </c>
-      <c r="AV3">
-        <v>2</v>
-      </c>
-      <c r="AW3">
-        <v>9</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>177</v>
-      </c>
       <c r="AY3">
         <v>0</v>
       </c>
@@ -12631,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -12640,7 +12529,7 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BI3">
         <v>1</v>
@@ -12652,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="BM3">
         <v>500000</v>
@@ -12682,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="CF3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="CG3">
         <v>0.05</v>
@@ -12697,10 +12586,10 @@
         <v>8</v>
       </c>
       <c r="CK3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -12709,28 +12598,28 @@
         <v>0</v>
       </c>
       <c r="CO3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CV3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="CW3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CX3">
         <v>96</v>
       </c>
       <c r="CY3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CZ3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="DA3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="DB3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DC3">
         <v>0</v>
@@ -12766,7 +12655,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -12924,7 +12813,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -12942,22 +12831,22 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>32100000</v>
+        <v>13100000</v>
       </c>
       <c r="L2" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="M2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -12966,7 +12855,7 @@
         <v>9</v>
       </c>
       <c r="S2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -12978,10 +12867,10 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>16050000</v>
+        <v>6550000</v>
       </c>
       <c r="AR2">
-        <v>32100000</v>
+        <v>13100000</v>
       </c>
       <c r="AS2">
         <v>0.95</v>
@@ -12996,19 +12885,19 @@
         <v>1</v>
       </c>
       <c r="AW2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AX2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY2">
         <v>96</v>
       </c>
       <c r="AZ2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -13025,7 +12914,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13043,10 +12932,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>14000000</v>
+        <v>12300000</v>
       </c>
       <c r="L3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -13058,7 +12947,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -13067,7 +12956,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -13079,10 +12968,10 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>7000000</v>
+        <v>6150000</v>
       </c>
       <c r="AR3">
-        <v>14000000</v>
+        <v>12300000</v>
       </c>
       <c r="AS3">
         <v>0.95</v>
@@ -13097,19 +12986,19 @@
         <v>1</v>
       </c>
       <c r="AW3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AX3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY3">
         <v>96</v>
       </c>
       <c r="AZ3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB3">
         <v>0</v>
@@ -13126,7 +13015,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13144,22 +13033,22 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>59800000</v>
+        <v>40300000</v>
       </c>
       <c r="L4" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="N4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -13168,7 +13057,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -13180,10 +13069,10 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>29900000</v>
+        <v>20150000</v>
       </c>
       <c r="AR4">
-        <v>59800000</v>
+        <v>40300000</v>
       </c>
       <c r="AS4">
         <v>0.95</v>
@@ -13198,16 +13087,16 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AX4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY4">
         <v>96</v>
       </c>
       <c r="AZ4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA4">
         <v>12</v>
@@ -13227,7 +13116,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13245,22 +13134,22 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>15500000</v>
+        <v>76100000</v>
       </c>
       <c r="L5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -13269,7 +13158,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -13281,10 +13170,10 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>7750000</v>
+        <v>38050000</v>
       </c>
       <c r="AR5">
-        <v>15500000</v>
+        <v>76100000</v>
       </c>
       <c r="AS5">
         <v>0.95</v>
@@ -13299,19 +13188,19 @@
         <v>1</v>
       </c>
       <c r="AW5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AX5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY5">
         <v>96</v>
       </c>
       <c r="AZ5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA5">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -13328,7 +13217,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13346,16 +13235,16 @@
         <v>1</v>
       </c>
       <c r="AG6">
-        <v>20000</v>
+        <v>38800</v>
       </c>
       <c r="AH6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -13364,7 +13253,7 @@
         <v>9</v>
       </c>
       <c r="AM6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -13376,19 +13265,19 @@
         <v>1</v>
       </c>
       <c r="AW6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AX6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY6">
         <v>96</v>
       </c>
       <c r="AZ6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -13405,7 +13294,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13423,16 +13312,16 @@
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>38100</v>
+        <v>20000</v>
       </c>
       <c r="AH7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AK7">
         <v>2</v>
@@ -13441,7 +13330,7 @@
         <v>9</v>
       </c>
       <c r="AM7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AN7">
         <v>0</v>
@@ -13453,16 +13342,16 @@
         <v>1</v>
       </c>
       <c r="AW7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AX7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY7">
         <v>96</v>
       </c>
       <c r="AZ7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA7">
         <v>60</v>
@@ -13501,7 +13390,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -13537,64 +13426,64 @@
         <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>137</v>
@@ -13623,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -13641,10 +13530,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>852000</v>
+        <v>891000</v>
       </c>
       <c r="L2">
-        <v>5380000</v>
+        <v>4800000</v>
       </c>
       <c r="M2">
         <v>0.95</v>
@@ -13659,19 +13548,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM2">
         <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AP2">
         <v>0</v>
@@ -13688,7 +13577,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13706,10 +13595,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1056000</v>
+        <v>1147000</v>
       </c>
       <c r="L3">
-        <v>4310000</v>
+        <v>4360000</v>
       </c>
       <c r="M3">
         <v>0.95</v>
@@ -13724,16 +13613,16 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM3">
         <v>96</v>
       </c>
       <c r="AN3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO3">
         <v>48</v>
@@ -13753,7 +13642,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13771,10 +13660,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1875000</v>
+        <v>2458000</v>
       </c>
       <c r="L4">
-        <v>8240000</v>
+        <v>8880000</v>
       </c>
       <c r="M4">
         <v>0.95</v>
@@ -13789,19 +13678,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM4">
         <v>96</v>
       </c>
       <c r="AN4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -13818,7 +13707,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13836,10 +13725,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>2150000000</v>
+        <v>2254000000</v>
       </c>
       <c r="V5">
-        <v>9790000000</v>
+        <v>6300000000</v>
       </c>
       <c r="W5">
         <v>0.95</v>
@@ -13854,19 +13743,19 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM5">
         <v>96</v>
       </c>
       <c r="AN5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -13883,7 +13772,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13901,10 +13790,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1150000000</v>
+        <v>863000000</v>
       </c>
       <c r="V6">
-        <v>5090000000</v>
+        <v>5960000000</v>
       </c>
       <c r="W6">
         <v>0.95</v>
@@ -13919,19 +13808,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM6">
         <v>96</v>
       </c>
       <c r="AN6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -13948,7 +13837,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13966,10 +13855,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1160000000</v>
+        <v>950000000</v>
       </c>
       <c r="V7">
-        <v>4320000000</v>
+        <v>4330000000</v>
       </c>
       <c r="W7">
         <v>0.95</v>
@@ -13984,19 +13873,19 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM7">
         <v>96</v>
       </c>
       <c r="AN7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -14013,7 +13902,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>96</v>
@@ -14031,10 +13920,10 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>201100000</v>
+        <v>89200000</v>
       </c>
       <c r="AF8">
-        <v>668000000</v>
+        <v>517000000</v>
       </c>
       <c r="AG8">
         <v>0.95</v>
@@ -14049,19 +13938,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM8">
         <v>96</v>
       </c>
       <c r="AN8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -14078,7 +13967,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F9">
         <v>96</v>
@@ -14096,10 +13985,10 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>90500000</v>
+        <v>157400000</v>
       </c>
       <c r="AF9">
-        <v>476000000</v>
+        <v>802000000</v>
       </c>
       <c r="AG9">
         <v>0.95</v>
@@ -14114,19 +14003,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM9">
         <v>96</v>
       </c>
       <c r="AN9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO9">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -14143,7 +14032,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F10">
         <v>96</v>
@@ -14161,10 +14050,10 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>94300000</v>
+        <v>95700000</v>
       </c>
       <c r="AF10">
-        <v>561000000</v>
+        <v>582000000</v>
       </c>
       <c r="AG10">
         <v>0.95</v>
@@ -14179,19 +14068,19 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AL10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM10">
         <v>96</v>
       </c>
       <c r="AN10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AP10">
         <v>0</v>
